--- a/artfynd/A 4532-2024 artfynd.xlsx
+++ b/artfynd/A 4532-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4532-2024 artfynd.xlsx
+++ b/artfynd/A 4532-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>112310557</v>
       </c>
       <c r="B2" t="n">
-        <v>94348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -716,7 +711,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518897</v>
+        <v>518896</v>
       </c>
       <c r="R2" t="n">
         <v>6736853</v>
@@ -803,15 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112310255</v>
+        <v>113629736</v>
       </c>
       <c r="B3" t="n">
-        <v>55682</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,48 +809,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kallesbacken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518860</v>
+        <v>518912</v>
       </c>
       <c r="R3" t="n">
-        <v>6736874</v>
+        <v>6736845</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,12 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Uppskrämd</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,22 +898,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Uno Skog, Anton Björk, Holger Martinussen</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113629736</v>
+        <v>112310651</v>
       </c>
       <c r="B4" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -950,34 +916,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kallesbacken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518912</v>
+        <v>518939</v>
       </c>
       <c r="R4" t="n">
-        <v>6736845</v>
+        <v>6736811</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +976,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +986,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På både sälg och rönn.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,6 +1003,21 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1039,10 +1026,136 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>Uno Skog, Anton Björk, Holger Martinussen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112310255</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kallesbacken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>518861</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6736874</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bjursås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Uppskrämd</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Uno Skog</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Uno Skog, Anton Björk, Holger Martinussen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4532-2024 artfynd.xlsx
+++ b/artfynd/A 4532-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112310557</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113629736</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1030,6 +1045,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112310651</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1156,8 +1176,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112310255</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>